--- a/transferability/output/tables/transferability_summary.xlsx
+++ b/transferability/output/tables/transferability_summary.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,45 +435,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>constraint_adjusted_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>weakest_link_gap</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>expected_mobilization_ratio</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>expected_risk_premium_bps</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>issuance_probability</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>adaptation_time_months</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>main_binding_constraint</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>lowest_pillar_score</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>transferability_grade</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>adaptation_track</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>source_type</t>
         </is>
@@ -492,36 +502,42 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>4.29900614802539</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>299.9950183093134</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>0.9664307767185175</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>9</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>legal_enforceability</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>65</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Near-term transferable</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>near-term</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -540,36 +556,42 @@
         <v>6.549999999999997</v>
       </c>
       <c r="D3" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>4.22247033950762</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>322.9844677802243</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0.9291694027586801</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>14.24</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>legal_enforceability</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>65</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Near-term transferable</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>near-term</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -588,36 +610,42 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
+        <v>69</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>4.191563271396756</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>331.8955045041025</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>0.907207046882843</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>16.2</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>legal_enforceability</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>62</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Transferable with adaptation</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>near-term</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -636,36 +664,42 @@
         <v>18.65</v>
       </c>
       <c r="D5" t="n">
-        <v>4.076424952293213</v>
+        <v>58.1</v>
       </c>
       <c r="E5" t="n">
-        <v>365.129145313081</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7543595074357308</v>
+        <v>4.036424952293213</v>
       </c>
       <c r="G5" t="n">
+        <v>372.629145313081</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7255179606769018</v>
+      </c>
+      <c r="I5" t="n">
         <v>23.92</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>public_finance_compatibility</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>55</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Transferable with adaptation</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>near-term</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -684,36 +718,42 @@
         <v>22.95</v>
       </c>
       <c r="D6" t="n">
-        <v>4.024597655753639</v>
+        <v>52.05</v>
       </c>
       <c r="E6" t="n">
-        <v>380.4178101523053</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6470278089459084</v>
+        <v>3.928597655753638</v>
       </c>
       <c r="G6" t="n">
+        <v>398.4178101523053</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5611917209472043</v>
+      </c>
+      <c r="I6" t="n">
         <v>33.36</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>legal_enforceability</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>48</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Transferable with adaptation</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Capacity-building before transfer</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>medium-term</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -732,36 +772,42 @@
         <v>30.7</v>
       </c>
       <c r="D7" t="n">
-        <v>3.931079086950062</v>
+        <v>42.8</v>
       </c>
       <c r="E7" t="n">
-        <v>407.459749659704</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4197012277108515</v>
+        <v>3.787079086950061</v>
       </c>
       <c r="G7" t="n">
+        <v>434.459749659704</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2965043090481888</v>
+      </c>
+      <c r="I7" t="n">
         <v>39.56</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>legal_enforceability</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>42</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Capacity-building before transfer</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>medium-term</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -780,36 +826,42 @@
         <v>37.35</v>
       </c>
       <c r="D8" t="n">
-        <v>3.851407592817067</v>
+        <v>34.4</v>
       </c>
       <c r="E8" t="n">
-        <v>430.462861347671</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2456404925642693</v>
+        <v>3.651407592817067</v>
       </c>
       <c r="G8" t="n">
+        <v>467.9628613476709</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1333104754333704</v>
+      </c>
+      <c r="I8" t="n">
         <v>50.88</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>public_finance_compatibility</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>35</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Capacity-building before transfer</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Foundation-building first</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>long-term</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -828,36 +880,42 @@
         <v>43.9</v>
       </c>
       <c r="D9" t="n">
-        <v>3.772360720335092</v>
+        <v>25.35</v>
       </c>
       <c r="E9" t="n">
-        <v>453.5457332264053</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1292057085071662</v>
+        <v>3.492360720335093</v>
       </c>
       <c r="G9" t="n">
+        <v>506.0457332264053</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.04935976830987477</v>
+      </c>
+      <c r="I9" t="n">
         <v>56.12</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>sustainable_finance_market_maturity</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>25</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Foundation-building first</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>long-term</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
@@ -876,36 +934,42 @@
         <v>49.75</v>
       </c>
       <c r="D10" t="n">
-        <v>3.703097330905187</v>
+        <v>18.25</v>
       </c>
       <c r="E10" t="n">
-        <v>474.0848433581265</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0684976037243261</v>
+        <v>3.383097330905187</v>
       </c>
       <c r="G10" t="n">
+        <v>534.0848433581267</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02166826631696053</v>
+      </c>
+      <c r="I10" t="n">
         <v>72.80000000000001</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>public_finance_compatibility</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Foundation-building first</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Indirect / very long-term transfer</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>indirect/very long-term</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>DERIVED_DATA</t>
         </is>
